--- a/presentations/heatmap_byhand/xlsx/baseline_methods/owasp_risk_rating/risk_ranking_filesystemMCP_owasp.xlsx
+++ b/presentations/heatmap_byhand/xlsx/baseline_methods/owasp_risk_rating/risk_ranking_filesystemMCP_owasp.xlsx
@@ -5633,12 +5633,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
     <col width="42" customWidth="1" min="2" max="2"/>
     <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="72" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1" ht="20.1" customHeight="1">
@@ -5657,6 +5658,11 @@
           <t>Risk Level</t>
         </is>
       </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Reasoning</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="13" t="n">
@@ -5672,6 +5678,11 @@
           <t>Critical</t>
         </is>
       </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>L=(7+8+7+9)/4=7.75(High); I=(9+1+9+1)/2=max(9,9)=9.0(High); matrix(H,H) → Critical</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="13" t="n">
@@ -5687,6 +5698,11 @@
           <t>Critical</t>
         </is>
       </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>L=(7+8+7+9)/4=7.75(High); I tech=9+1=9(capped) biz=9+1=9; matrix(H,H) → Critical</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="13" t="n">
@@ -5702,6 +5718,11 @@
           <t>Critical</t>
         </is>
       </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>L=(7+7+7+9)/4=7.5(High); I tech=9 biz=9; matrix(H,H) → Critical</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="9" t="n">
@@ -5717,6 +5738,11 @@
           <t>Critical</t>
         </is>
       </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>L=(7+7+8+9)/4=7.75(High); I tech=9+0=9 biz=9+0=9; matrix(H,H) → Critical</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="11" t="n">
@@ -5732,6 +5758,11 @@
           <t>Critical</t>
         </is>
       </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>L=(7+6+8+9)/4=7.5(High); I tech=9-1=8 biz=9-0=9; matrix(H,H) → Critical</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="9" t="n">
@@ -5747,6 +5778,11 @@
           <t>Critical</t>
         </is>
       </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>L=(7+7+8+9)/4=7.75(High); I tech=9-2=7 biz=9-0=9; matrix(H,H) → Critical</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="9" t="n">
@@ -5762,6 +5798,11 @@
           <t>High</t>
         </is>
       </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>L=(7+5+8+9)/4=7.25(High); I tech=9-4=5(Med) biz=9-3=6(High); matrix(H,H) → Critical</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="11" t="n">
@@ -5775,6 +5816,11 @@
       <c r="C9" s="12" t="inlineStr">
         <is>
           <t>Critical</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>L=(7+5+8+9)/4=7.25(High); I tech=9-3=6(High) biz=9-2=7(High); matrix(H,H) → Critical</t>
         </is>
       </c>
     </row>
@@ -5795,7 +5841,7 @@
     <col width="5.28515625" bestFit="1" customWidth="1" min="1" max="1"/>
     <col width="6.28515625" bestFit="1" customWidth="1" min="2" max="2"/>
     <col width="9.7109375" bestFit="1" customWidth="1" min="3" max="3"/>
-    <col width="50.5703125" bestFit="1" customWidth="1" min="4" max="4"/>
+    <col width="72" bestFit="1" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6071,11 +6117,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5.28515625" bestFit="1" customWidth="1" min="1" max="1"/>
     <col width="14.7109375" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="72" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6094,6 +6141,11 @@
           <t>Risk Level</t>
         </is>
       </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Reasoning</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="13" t="n">
@@ -6109,6 +6161,11 @@
           <t>Critical</t>
         </is>
       </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>dir base (tech=9,biz=9); write I=(9+1)cap=9, L=7.75 High → Critical</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="13" t="n">
@@ -6124,6 +6181,11 @@
           <t>Critical</t>
         </is>
       </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>dir base (9,9); all tools L≥7.25 High; I≥6.0 High → Critical</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="13" t="n">
@@ -6139,6 +6201,11 @@
           <t>Critical</t>
         </is>
       </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>dir base (8,7); write I=(8+1,7+1) High; L=High → Critical</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="9" t="n">
@@ -6154,6 +6221,11 @@
           <t>Critical</t>
         </is>
       </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>dir base (7,6); write I=(7+1,6+1) High; L=High → Critical</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="11" t="n">
@@ -6169,6 +6241,11 @@
           <t>Critical</t>
         </is>
       </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>dir base (7,7); write I=High; L=High → Critical</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="9" t="n">
@@ -6184,6 +6261,11 @@
           <t>Critical</t>
         </is>
       </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>dir base (7,6); write I=High; L=High → Critical</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="11" t="n">
@@ -6199,6 +6281,11 @@
           <t>Critical</t>
         </is>
       </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>dir base (6,6); write I=(6+1,6+1)=(7,7) High; L=High → Critical</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="9" t="n">
@@ -6214,7 +6301,13 @@
           <t>High</t>
         </is>
       </c>
-    </row>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>dir base (3,4); write I=(3+1,4+1)=(4,5) Med; L=High → High</t>
+        </is>
+      </c>
+    </row>
+    <row r="10"/>
     <row r="11">
       <c r="B11" t="inlineStr">
         <is>
